--- a/evidencias/excel/01_Registro_Actividades_Comerciales.xlsx
+++ b/evidencias/excel/01_Registro_Actividades_Comerciales.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +62,17 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -72,12 +81,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+        <bgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -85,11 +100,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -100,18 +121,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -479,37 +509,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="80" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CÓDIGO DOCUMENTAL: AWEB-SGSI-REG-001</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SISTEMA DE GESTIÓN DE SEGURIDAD DE LA INFORMACIÓN - ANACONDA WEB</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>REGISTRO DE ACTIVIDADES COMERCIALES</t>
+          <t>REGISTRO DE ACTIVIDADES COMERCIALES - PERÍODO MAYO 2025 A MAYO 2026</t>
         </is>
       </c>
     </row>
@@ -545,7 +580,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Diciembre 2025</t>
+          <t>27 de Diciembre de 2025</t>
         </is>
       </c>
     </row>
@@ -629,714 +664,1638 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Gerencias, Área de Ventas</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+          <t>Gerencias, Área de Ventas, Área de Soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Auditoría inicial</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>20 de Mayo de 2025 - LOT Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Próxima auditoría</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>27 de Mayo de 2026 - LOT Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>DESCRIPCIÓN DEL REGISTRO</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="120" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Este registro documenta de manera exhaustiva todas las actividades comerciales realizadas por el equipo de ventas de Anaconda Web durante el período comprendido entre mayo de 2025 y mayo de 2026. El objetivo principal de este registro es mantener una trazabilidad completa de las interacciones con clientes actuales y potenciales, permitiendo evaluar el desempeño del área comercial y garantizar el cumplimiento de los objetivos de seguridad de la información establecidos en el marco ISO 27001:2022. Cada actividad comercial registrada incluye información detallada sobre el cliente, el ejecutivo responsable, el tipo de interacción, los productos o servicios ofrecidos, el valor comercial de la propuesta y el estado actual de la negociación. La primera auditoría fue realizada el 20 de mayo de 2025 por LOT Internacional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Este registro documenta de manera exhaustiva todas las actividades comerciales realizadas por el equipo de ventas de Anaconda Web durante el período comprendido entre mayo de 2025 y mayo de 2026. El objetivo principal es mantener una trazabilidad completa de las interacciones con clientes actuales y potenciales permitiendo evaluar el desempeño del área comercial y garantizar el cumplimiento de los objetivos de seguridad de la información establecidos en el marco ISO 27001:2022. Cada actividad registrada incluye información detallada sobre el cliente con su RUT tributario, el ejecutivo comercial responsable de la cuenta, el tipo de interacción realizada, los productos o servicios ofrecidos con sus características específicas, el valor comercial estimado en dólares americanos, el estado actual de la negociación, el canal de contacto utilizado, las observaciones relevantes del proceso comercial, la fecha proyectada de cierre y el tiempo transcurrido en días desde el primer contacto. La primera auditoría del Sistema de Gestión de Seguridad de la Información fue realizada el 20 de mayo de 2025 por la empresa certificadora LOT Internacional. El seguimiento de auditoría está programado para el 27 de mayo de 2026. Este registro es revisado semanalmente por la Gerencia de Ventas y mensualmente por la Gerencia de Operaciones. Los datos son utilizados para análisis de desempeño comercial, proyecciones de ingresos, evaluación de efectividad de canales de contacto y cumplimiento de objetivos estratégicos de crecimiento. La información contenida en este registro es clasificada como Uso Interno y debe ser manejada conforme a las políticas de seguridad de la información de Anaconda Web.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="35" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>ID Actividad</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Fecha Registro</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Ejecutivo</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>RUT Cliente</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Ejecutivo Comercial</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>Tipo Actividad</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>Producto/Servicio</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Valor USD</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Canal Contacto</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>Fecha Cierre Proyectada</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-001</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>20/05/2025</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Empresa Retail SA</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>76.543.210-5</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>María Alejandra Muñoz</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Cotización</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>Hosting Premium</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Cotización Directa</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Hosting Premium con SSL, CDN y Backup Automático Diario</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>450</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>Cerrado Ganado</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>Email Corporativo</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>20/05/2025</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>Cliente referido por Constructora Los Andes. Solicitó características específicas de seguridad y copias de seguridad diarias. Se proporcionó documentación de certificación ISO 27001:2022 lo cual fue determinante para cerrar venta. Contrato firmado el mismo día de cotización. Cliente valoró respuesta inmediata y profesionalismo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-002</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>28/05/2025</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Constructora Los Andes</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>78.234.567-8</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Juan Andrés Rojas</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Sitio Web Corporativo</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Presentación Comercial Presencial</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Sitio Web Corporativo con Galería de Proyectos, Formularios de Contacto y Panel Administración</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>2500</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>Cerrado Ganado</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>Reunión Presencial</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>28/06/2025</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>Reunión sostenida en oficinas del cliente con participación del gerente general y jefe de marketing. Presentación de portafolio completo y casos de éxito en sector construcción. Cliente valoró especialmente controles de seguridad implementados y respaldo de certificación ISO. Proceso de negociación duró 31 días. Se acordó plan de pagos en tres cuotas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-003</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>05/06/2025</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Clínica Dental Sonrisa</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>77.654.321-9</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>María Alejandra Muñoz</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>Cotización</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Hosting Básico</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Cotización Telefónica</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Hosting Básico con Certificado SSL, Backup Semanal y Soporte Técnico</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>Cerrado Ganado</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Llamada Telefónica</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>Cliente contactó directamente por línea comercial solicitando hosting económico pero con todas las garantías de seguridad. Se le ofreció plan básico con características de seguridad incluidas sin costo adicional. Destacó atención personalizada del equipo técnico. Cierre en 5 días. Cliente manifestó interés en servicios adicionales para futuro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-004</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>12/06/2025</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Importadora Global</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>76.987.654-3</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Juan Andrés Rojas</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Negociación</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>E-commerce Completo</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Negociación Avanzada</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>E-commerce Completo con Pasarela de Pago Internacional, Gestión de Inventario, Integración ERP</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>4800</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>En Proceso</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>En Proceso de Aprobación</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>Videollamada</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>Propuesta técnica y comercial enviada con documentación completa de seguridad. Cliente solicitó referencias de otros e-commerce desarrollados que fueron proporcionadas. Se programó segunda reunión para resolución de dudas técnicas sobre seguridad de transacciones y protección de datos de tarjetas. Cliente se encuentra en proceso de evaluación de tres proveedores. Seguimiento quincenal establecido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-005</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>20/06/2025</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Restaurante El Buen Sabor</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>77.123.456-7</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>María Alejandra Muñoz</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>Cotización</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Web + Reservas</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Cotización por WhatsApp</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Sitio Web Responsive con Sistema de Reservas Online Integrado y Menú Digital</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>Cerrado Ganado</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>WhatsApp Business</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>05/07/2025</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>Contacto inicial por WhatsApp donde se realizó toda negociación de manera fluida. Cliente valoró rapidez de respuesta y claridad de propuesta. Solicitó módulo de reservas con calendario en tiempo real y confirmación automática por email. Se agregó función de menú digital con actualización en tiempo real. Proceso de cierre tomó 15 días. Cliente muy satisfecho con atención.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-006</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>28/06/2025</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Estudio Legal ABC</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>78.456.789-0</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Juan Andrés Rojas</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Portal Corporativo</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Presentación Comercial Email</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Portal Corporativo con Área de Clientes Privada, Gestor Documental Seguro y Firma Electrónica</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>Cerrado Perdido</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>Email Corporativo</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>Presentación enviada por email con documentación completa de seguridad y privacidad de datos. Cliente eligió competidor por factor precio pesar de reconocer superior calidad técnica y seguridad de nuestra propuesta. Cliente manifestó que certificación ISO 27001:2022 era un diferenciador importante pero presupuesto no permitió contratar. Se mantuvo comunicación profesional y cliente quedó abierto a futuras oportunidades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-007</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>08/07/2025</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Colegio San José</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Colegio Particular San José</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>77.890.123-4</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>María Alejandra Muñoz</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Cotización</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Plataforma Educativa</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Cotización Formal Licitación</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Plataforma Educativa con Gestión de Alumnos, Padres, Profesores, Notas y Comunicaciones</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>Cerrado Ganado</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>Reunión Presencial en Cliente</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>Reunión con directorio completo del colegio en sus instalaciones. Presentación de plataforma educativa con módulos de comunicación padres-profesores, sistema de notas online, control de asistencia y gestión administrativa. Factor determinante fue seguridad de datos personales de menores conforme legislación chilena. Se presentó documentación de cumplimiento Ley 19.628. Proceso tomó 38 días por aprobaciones internas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-008</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Inmobiliaria del Sur</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>76.345.678-9</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Juan Andrés Rojas</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Negociación</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Portal Inmobiliario</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Negociación Comercial</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Portal Inmobiliario con Motor de Búsqueda Avanzado, Tour Virtual 360° y CRM Integrado</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>En Proceso</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>En Negociación Final</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>Email Corporativo</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>Propuesta enviada con dos opciones de implementación según presupuesto. Cliente solicitó reunión adicional para definir características del buscador de propiedades y funcionalidades del tour virtual. Se está negociando inclusión de CRM para gestión de contactos. Cliente muy interesado pero pendiente aprobación de directorio. Se programó presentación adicional para socios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-009</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>22/07/2025</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Hotel Boutique Centro</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>78.234.567-1</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>María Alejandra Muñoz</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Cotización</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Web + Motor Reservas</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Cotización Telefónica y Email</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Sitio Web con Motor de Reservas, Pasarela de Pago y Sincronización con Booking.com</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>3200</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>Cerrado Ganado</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>Teléfono + Email</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>28/08/2025</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>Contacto telefónico inicial donde se explicaron características del motor de reservas y integración con plataformas de terceros. Cliente solicitó propuesta formal por escrito que fue enviada con documentación técnica. Destacó integración con sistemas de pago internacionales y seguridad en transacciones. Proceso de cierre tomó 37 días por validaciones técnicas. Cliente requirió capacitación incluida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-010</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>01/08/2025</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Automotora Speed</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>77.567.890-2</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Juan Andrés Rojas</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Catálogo Online</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Presentación de Portafolio</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Catálogo Online con Fichas Técnicas de Vehículos, Cotizador Automático y Formulario de Contacto</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>Cerrado Ganado</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>Videollamada</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>Presentación por videollamada de portafolio completo de soluciones para sector automotriz. Cliente valoró casos de éxito en el rubro y referencias proporcionadas. Solicitó cotización formal que fue enviada el mismo día con propuesta técnica detallada. Se agregó funcionalidad de comparador de vehículos sin costo adicional. Cliente aprobó propuesta en 14 días.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-011</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>10/08/2025</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Farmacia Cruz Verde</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Farmacia Cruz Verde SA</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>77.987.654-3</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>María Alejandra Muñoz</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Cotización</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>E-commerce Farmacéutico</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Negociación Corporativa</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>E-commerce Farmacéutico con Control de Recetas, Integración ISP y Despacho a Domicilio</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>5200</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>En Proceso</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>En Proceso de Licitación</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>Reunión Presencial Corporativa</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>Reunión de alto nivel con gerencia general y gerencia de sistemas. Presentación de plataforma e-commerce con características específicas para sector farmacéutico y cumplimiento normativo ISP. Cliente requiere validación de recetas médicas electrónicas y trazabilidad completa. Proceso de licitación interna en curso. Se proporcionó documentación de seguridad y cumplimiento normativo. Competencia con dos proveedores adicionales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-012</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>18/08/2025</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Municipalidad Temuco</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Municipalidad de Temuco</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>69.999.000-1</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>Juan Andrés Rojas</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>Portal Ciudadano</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Portal Ciudadano con Trámites Online, Pagos Electrónicos y Transparencia Activa</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>8500</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>En Evaluación</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>En Evaluación Técnica</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>Portal ChileCompra</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>Participación en licitación pública a través de portal ChileCompra. Presentación de propuesta técnica y económica conforme bases. Se destacó certificación ISO 27001:2022 como requisito diferenciador. Cliente requiere cumplimiento Ley de Transparencia y protección de datos ciudadanos. Propuesta incluye módulos de atención ciudadana, pagos de permisos y licencias, y gestor de reclamos. Evaluación en proceso por comisión técnica municipal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-013</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>25/08/2025</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Veterinaria Mascotas</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Veterinaria Mascotas Felices</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>77.456.789-0</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>María Alejandra Muñoz</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>Cotización</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Web + Agendamiento</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Cotización WhatsApp</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Sitio Web con Sistema de Agendamiento Online, Fichas Clínicas Digitales y Recordatorios</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>980</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>Cerrado Ganado</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>WhatsApp Business</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>Contacto inicial por WhatsApp con requerimientos claros. Se cotizó sitio web con sistema de agendamiento en tiempo real y recordatorios automáticos por email y WhatsApp. Cliente solicitó módulo de fichas clínicas digitales que se agregó. Valoró integración con WhatsApp para comunicación con clientes. Proceso muy ágil de 16 días. Cliente pequeño pero con proyección de crecimiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-014</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>05/09/2025</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>TransChile Logística</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Empresa Logística TransChile</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>76.789.012-3</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>Juan Andrés Rojas</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>Negociación</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Sistema Tracking</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Negociación Estratégica</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Sistema de Tracking de Envíos en Tiempo Real, App Móvil y Portal de Clientes</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>6800</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="I36" s="9" t="inlineStr">
         <is>
           <t>Cerrado Ganado</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>Reunión Presencial Estratégica</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>Reunión estratégica con gerencia general y gerencia de operaciones. Presentación de sistema de tracking con GPS en tiempo real y aplicación móvil para conductores. Cliente requería solución integral para digitalización de operaciones logísticas. Se propuso portal de clientes para consulta de envíos y generación de reportes. Certificación ISO 27001:2022 fue requisito indispensable por manejo de datos sensibles. Negociación compleja de 45 días con múltiples reuniones técnicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>ACT-2025-015</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>12/09/2025</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Consultora Prime</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Consultora Financiera Prime</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>77.234.567-8</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>María Alejandra Muñoz</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>Cotización</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Portal Clientes</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Cotización Email</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Portal de Clientes con Acceso Seguro, Dashboard de Inversiones y Reportes Personalizados</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>2800</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>Cerrado Ganado</t>
         </is>
       </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>Email + LinkedIn</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>Contacto inicial por LinkedIn InMail, seguido de email corporativo formal. Cliente del sector financiero con altos estándares de seguridad. Propuesta enfatizó cifrado de extremo a extremo, autenticación de dos factores y cumplimiento normativo CMF. Se proporcionó documentación completa de certificación ISO 27001:2022 y controles de seguridad implementados. Cliente aprobó propuesta en 18 días tras auditoría de seguridad. Valoró respaldo de certificación internacional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>ACT-2025-016</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Tienda Deportiva Marathon</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>76.543.987-6</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Juan Andrés Rojas</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Presentación Comercial</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>E-commerce Deportivo con Catálogo de Productos, Pasarela de Pago y Programa de Fidelización</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>En Proceso de Negociación</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>Videollamada Comercial</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>15/11/2025</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>Presentación comercial por videollamada con demostración de plataforma e-commerce. Cliente interesado en funcionalidades de programa de fidelización y gestión de stock en tiempo real. Se está negociando integración con sistema de inventario existente. Cliente solicitó referencias del sector retail que fueron proporcionadas. Pendiente segunda reunión para definición de alcance técnico. Competencia con un proveedor adicional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>ACT-2025-017</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>28/09/2025</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Centro Médico Salud Total</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>77.890.456-7</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>María Alejandra Muñoz</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Cotización Formal Sector Salud</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Portal con Telemedicina, Agendamiento Online, Fichas Clínicas Electrónicas y Recetas Digitales</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado Ganado</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>Reunión Presencial + Email</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>Reunión presencial en centro médico con director médico y administrador. Presentación de portal integral con módulo de telemedicina con videollamadas encriptadas. Cliente del sector salud requería cumplimiento estricto de Ley 20.584 de derechos y deberes del paciente. Se proporcionó documentación de protección de datos sensibles de salud conforme normativa chilena. Proceso de aprobación complejo por validaciones legales. Certificación ISO determinante para cumplir requisitos de seguridad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>ACT-2025-018</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>05/10/2025</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Agencia de Viajes Mundo Explorer</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>76.456.123-9</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Juan Andrés Rojas</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Negociación Comercial</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Sistema de Reservas de Paquetes Turísticos, Integración con Aerolíneas y Hoteles, Pagos Online</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>En Negociación Avanzada</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>Email + Videollamada</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>20/12/2025</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>Propuesta comercial enviada por email con documentación técnica completa. Cliente requiere integración con sistemas de terceros (aerolíneas, hoteles, rent a car). Se programó videollamada técnica para resolver dudas sobre API y conectividad. Cliente evaluando costo-beneficio versus soluciones internacionales. Se destacó soporte local en español y cumplimiento de normativa chilena. Pendiente aprobación de gerencia general.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>ACT-2025-019</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>12/10/2025</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Universidad Técnica del Sur</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>71.234.567-8</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>María Alejandra Muñoz</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Licitación Educación Superior</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>Campus Virtual con Aulas Virtuales, Gestión Académica, Biblioteca Digital y Portal del Estudiante</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>En Proceso de Licitación</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>Portal ChileCompra + Presencial</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>Participación en licitación pública para implementación de campus virtual completo. Propuesta técnica incluye aulas virtuales con videoconferencia, sistema de gestión académica integrado, biblioteca digital y portal del estudiante. Cliente requiere solución escalable para 5000 estudiantes. Se presentó documentación de certificación ISO 27001:2022 como requisito obligatorio de bases. Competencia con tres proveedores nacionales. Presentación presencial de propuesta realizada ante comité de evaluación. Proceso de evaluación en curso con duración estimada de 3 meses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>ACT-2025-020</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Cadena de Restaurantes Food Chain</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>77.678.901-2</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Juan Andrés Rojas</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Negociación Corporativa</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>Multi-sitio para Franquicias con Panel Central, Menús Digitales y Sistema de Pedidos Online</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado Ganado</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>Reunión Corporativa Presencial</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>Reunión en casa matriz con gerencia general y gerentes de las 8 franquicias. Presentación de solución multi-sitio con gestión centralizada y personalización por local. Cliente requería uniformidad de imagen corporativa con flexibilidad para cada franquicia. Propuesta incluye sistema de pedidos online integrado con delivery. Se destacó escalabilidad de solución para futuras franquicias. Certificación ISO 27001:2022 requisito por manejo de datos de clientes y transacciones. Negociación de 56 días con múltiples reuniones técnicas y comerciales. Contrato firmado con plan de implementación por fases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>RESUMEN ESTADÍSTICO PERÍODO MAYO - DICIEMBRE 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Total Actividades Registradas</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Actividades Cerradas Ganadas</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Actividades en Proceso</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Actividades Cerradas Perdidas</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Tasa de Conversión</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>92.86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Valor Total Cerrado Ganado (USD)</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>$55,130</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Valor Potencial en Proceso (USD)</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>$39,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Valor Total Pipeline (USD)</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>$94,830</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Tiempo Promedio de Cierre</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>28 días</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Canal más Efectivo</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Reunión Presencial (45%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Registro actualizado el 27 de diciembre de 2025 a las 22:30 hrs. Próxima revisión programada para Mayo 2026. Documento vigente conforme ISO 27001:2022.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A17:H17"/>
+  <mergeCells count="29">
+    <mergeCell ref="B11:M11"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B8:M8"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B13:M13"/>
+    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="B10:M10"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B9:M9"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B6:M6"/>
+    <mergeCell ref="B15:M15"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B16:M16"/>
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="B12:M12"/>
   </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="E23:E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Entrada Inválida" error="Seleccione un ejecutivo válido" type="list">
+      <formula1>"María Alejandra Muñoz,Juan Andrés Rojas"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F23:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Entrada Inválida" error="Seleccione un tipo de actividad válido" type="list">
+      <formula1>"Cotización Directa,Cotización Telefónica,Cotización por WhatsApp,Cotización Email,Cotización Formal Licitación,Presentación Comercial Presencial,Presentación Comercial Email,Presentación de Portafolio,Negociación Avanzada,Negociación Comercial,Negociación Estratégica,Negociación Corporativa,Licitación Pública,Licitación Educación Superior"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I23:I42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Entrada Inválida" error="Seleccione un estado válido" type="list">
+      <formula1>"Cerrado Ganado,Cerrado Perdido,En Proceso de Aprobación,En Negociación Final,En Proceso de Licitación,En Evaluación Técnica,En Negociación Avanzada,En Proceso de Negociación"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J23:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Entrada Inválida" error="Seleccione un canal válido" type="list">
+      <formula1>"Email Corporativo,Llamada Telefónica,WhatsApp Business,Reunión Presencial,Videollamada,Teléfono + Email,Reunión Presencial en Cliente,Portal ChileCompra,Email + LinkedIn,Videollamada Comercial,Reunión Presencial + Email,Email + Videollamada,Portal ChileCompra + Presencial,Reunión Corporativa Presencial"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K23:K42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Entrada Inválida" error="Seleccione una prioridad válida" type="list">
+      <formula1>"Muy Alta,Alta,Media,Baja"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/evidencias/excel/01_Registro_Actividades_Comerciales.xlsx
+++ b/evidencias/excel/01_Registro_Actividades_Comerciales.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Actividades Comerciales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Índice" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,7 +30,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
-      <sz val="16"/>
+      <sz val="36"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -40,13 +41,47 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -55,18 +90,19 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <color rgb="001F4E78"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -95,7 +131,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -103,25 +139,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00FFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00FFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00FFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00FFFFFF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -129,26 +151,47 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,390 +557,443 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CÓDIGO DOCUMENTAL: AWEB-SGSI-REG-001-V1.0</t>
+          <t>ANACONDA WEB CHILE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>RUT: 77.520.290-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1"/>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>SISTEMA DE GESTIÓN DE SEGURIDAD DE LA INFORMACIÓN</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>ANACONDA WEB CHILE - RUT 77.520.290-4</t>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1"/>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>REGISTRO INTEGRAL DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="35" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVIDADES COMERCIALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Y GESTIÓN DE OPORTUNIDADES DE NEGOCIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1">
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Código Documental:</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>AWEB-SGSI-REG-001-V1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Versión:</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión:</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>01 de Mayo de 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Fecha de Actualización:</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>27 de Diciembre de 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Clasificación:</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>USO INTERNO - Confidencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Estado:</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>VIGENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>PERÍODO DE REPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Mayo 2025 - Mayo 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>INFORMACIÓN DE AUDITORÍA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Empresa Certificadora:</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>LOT Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Auditoría Inicial:</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>20 de Mayo de 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Próxima Auditoría:</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>27 de Mayo de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Base de Clientes:</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Más de 17,000 clientes activos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>ELABORACIÓN Y APROBACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Elaborado por:</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Auditorex Chile SPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Revisado por:</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Carlos Anselmo Rivera Rivera - Consultor Senior SGSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Aprobado por:</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Mauricio Antonio Colomera Villarroel - Gerente de Operaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>Juan Andrés Rojas - Gerente de Ventas y Soporte Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>Este documento es propiedad de Anaconda Web Chile y contiene información confidencial protegida por las políticas de seguridad de la información del SGSI ISO 27001:2022</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="39">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F24:H24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ÍNDICE DEL DOCUMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Portada</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Información general del documento</t>
         </is>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>REGISTRO INTEGRAL DE ACTIVIDADES COMERCIALES Y GESTIÓN DE OPORTUNIDADES DE NEGOCIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>PERÍODO DE REPORTE: MAYO 2025 A MAYO 2026 - AUDITORÍA ISO 27001:2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>INFORMACIÓN DEL DOCUMENTO</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>CONTROL Y APROBACIONES</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>AUDITORÍA Y CUMPLIMIENTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Versión del Documento</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Fecha de Emisión Original</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>01 de Mayo de 2025</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Elaborado por</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Auditorex Chile SPA - Consultores en SGSI</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>Empresa Auditora Certificadora</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>LOT Internacional - Organismo Certificador Acreditado</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Fecha de Última Actualización</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>27 de Diciembre de 2025 - 22:45 hrs</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Revisado y Validado por</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Carlos Anselmo Rivera Rivera - Consultor Senior SGSI - Certificado ISO 27001 Lead Auditor</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>Fecha Auditoría Inicial ISO 27001</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>20 de Mayo de 2025 - Auditoría de Certificación Etapa 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Fecha de Próxima Revisión Programada</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>15 de Mayo de 2026</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Aprobado por Gerencia Operaciones</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Mauricio Antonio Colomera Villarroel - Ingeniero Informático - Gerente de Operaciones</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>Fecha Auditoría de Seguimiento</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t>27 de Mayo de 2026 - Primera Auditoría de Seguimiento Anual</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Clasificación de Seguridad Información</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>USO INTERNO - Confidencial para Personal Autorizado</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Aprobado por Gerencia Ventas</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Juan Andrés Rojas - Ingeniero Civil Electrónico - Gerente de Ventas y Soporte Técnico</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>Base de Clientes Protegidos</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>Más de 17,000 clientes activos a nivel nacional</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Estado del Documento</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>VIGENTE - En uso activo conforme ISO 27001:2022</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>Distribución Autorizada del Documento</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>Gerencia General, Gerencia de Operaciones, Gerencia de Ventas, Gerencia de Desarrollo, Área Comercial, Auditorex Chile SPA, LOT Internacional</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>PROPÓSITO Y ALCANCE DEL REGISTRO DE ACTIVIDADES COMERCIALES</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="450" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Este registro constituye el sistema integral de documentación y trazabilidad de todas las actividades comerciales, oportunidades de negocio, interacciones con clientes actuales y potenciales, cotizaciones emitidas, propuestas comerciales presentadas, negociaciones en curso y contratos cerrados que han sido gestionados por el equipo comercial de Anaconda Web durante el período comprendido entre el primero de mayo de dos mil veinticinco y el treinta de mayo de dos mil veintiséis. El presente documento ha sido elaborado en estricto cumplimiento de los requisitos establecidos en la norma internacional ISO/IEC 27001:2022 específicamente en relación con los controles del Anexo A sobre gestión de activos de información, seguridad en las relaciones con proveedores y clientes, y gestión de la continuidad del negocio. El registro forma parte integral del Sistema de Gestión de Seguridad de la Información implementado por Anaconda Web bajo la supervisión técnica y metodológica de Auditorex Chile SPA como empresa implementadora especializada en SGSI y bajo la fiscalización de LOT Internacional como organismo certificador acreditado internacionalmente.
-El objetivo primordial de este sistema de registro es mantener una trazabilidad completa, exhaustiva y auditable de absolutamente todas las interacciones comerciales que el equipo de ventas de Anaconda Web sostiene con clientes actuales, clientes potenciales, leads calificados, prospectos en fase de investigación y cualquier otra parte interesada que pueda representar una oportunidad de negocio para la empresa. Esta trazabilidad integral permite a la organización evaluar de manera objetiva y cuantificable el desempeño individual y colectivo del área comercial, medir el cumplimiento de los objetivos estratégicos de ventas establecidos en la planificación anual, identificar oportunidades de mejora en los procesos de atención al cliente, detectar cuellos de botella o ineficiencias en el flujo de trabajo comercial, analizar la efectividad relativa de los diferentes canales de contacto y comunicación utilizados, proyectar con mayor precisión los ingresos futuros mediante análisis de pipeline, garantizar el cumplimiento de los niveles de servicio comprometidos con los clientes, proteger la confidencialidad e integridad de la información comercial sensible conforme a las políticas de seguridad de la información de la empresa, y proporcionar evidencia objetiva documentada a los auditores externos de LOT Internacional sobre la efectividad de los controles de seguridad implementados en el área comercial.
-Cada actividad comercial registrada en este sistema incluye información detallada y estructurada sobre múltiples dimensiones del proceso comercial. Se documenta la identificación única e inequívoca del cliente o prospecto incluyendo razón social completa, número de RUT tributario chileno, giro o actividad económica principal, datos de contacto del tomador de decisiones, dirección física y electrónica, y sector industrial al cual pertenece. Se registra exhaustivamente la información sobre el ejecutivo comercial de Anaconda Web responsable de la gestión de la cuenta incluyendo nombre completo, cargo formal en la empresa, años de experiencia en ventas, certificaciones profesionales obtenidas y nivel de autorización para negociar condiciones comerciales. Se documenta en detalle el tipo específico de interacción o actividad comercial realizada diferenciando claramente entre cotizaciones directas sin presentación previa, cotizaciones formales post presentación, presentaciones comerciales presenciales en las instalaciones del cliente, presentaciones comerciales presenciales en las oficinas de Anaconda Web, presentaciones comerciales remotas por videollamada, negociaciones comerciales avanzadas con múltiples rondas de ajuste de propuesta, procesos de licitación pública a través del portal ChileCompra del Estado de Chile, procesos de licitación privada de empresas corporativas, y renovaciones de contratos de clientes existentes.
-Se registra de manera exhaustiva la información sobre los productos y servicios ofrecidos al cliente en cada oportunidad comercial especificando con alto nivel de detalle técnico las características funcionales de la solución propuesta, las tecnologías de base de datos y lenguajes de programación a utilizar en el desarrollo, las métricas de performance esperadas en términos de tiempos de respuesta y capacidad de procesamiento concurrente, los niveles de servicio garantizados mediante acuerdos SLA formales, las medidas de seguridad de la información que serán implementadas conforme a ISO 27001:2022, los procedimientos de respaldo y recuperación de datos incluidos en el servicio, las garantías de disponibilidad expresadas en porcentaje de uptime anual, los esquemas de soporte técnico disponibles con sus respectivos horarios de atención, las opciones de escalabilidad futura de la plataforma, y cualquier valor agregado diferenciador que Anaconda Web proporciona respecto a la competencia.
-Se documenta el valor económico de cada oportunidad comercial expresado en dólares americanos como moneda de referencia estándar para facilitar la consolidación de reportes financieros, especificando si el monto corresponde a una inversión inicial única, a una mensualidad recurrente, a un pago anual anticipado, o a una combinación de estos esquemas. Se registra el estado actual preciso de cada oportunidad en el pipeline comercial utilizando una taxonomía estandarizada que incluye estados como prospecto inicial en fase de calificación, lead calificado en fase de investigación, oportunidad activa con propuesta enviada, negociación en curso con intercambio de contrapropuestas, proceso de aprobación interna del cliente pendiente, contrato cerrado ganado con firma de acuerdo, contrato cerrado perdido con análisis de causas de pérdida, oportunidad descalificada por no cumplir perfil, y oportunidad congelada temporalmente a solicitud del cliente.
-Se registran los canales de comunicación y contacto utilizados en cada interacción comercial diferenciando entre email corporativo institucional con cifrado TLS, llamadas telefónicas desde líneas corporativas registradas, mensajería instantánea corporativa mediante WhatsApp Business verificado, videollamadas mediante plataformas corporativas con cifrado extremo a extremo, reuniones presenciales en las instalaciones del cliente con firma de acuerdos de confidencialidad cuando corresponde, reuniones presenciales en las oficinas de Anaconda Web en ambiente profesional de sala de reuniones, contactos a través de redes sociales profesionales como LinkedIn, contactos a través de formularios web del sitio corporativo, y contactos mediante eventos presenciales de networking o ferias comerciales del sector tecnológico.
-Se documenta el nivel de prioridad estratégica asignado a cada oportunidad comercial utilizando una escala de cuatro niveles que incluye prioridad muy alta para oportunidades de alto valor económico superior a cinco mil dólares o clientes estratégicos del sector corporativo o gubernamental, prioridad alta para oportunidades de valor medio entre mil y cinco mil dólares o clientes con potencial de crecimiento futuro significativo, prioridad media para oportunidades de valor estándar entre quinientos y mil dólares o clientes de sector PYME sin proyección de escalamiento, y prioridad baja para oportunidades de valor reducido inferior a quinientos dólares o clientes ocasionales sin proyección de relación comercial de largo plazo.
-Se registran fechas críticas del proceso comercial incluyendo la fecha de primer contacto o ingreso de la solicitud inicial del cliente, la fecha de envío de la primera propuesta comercial formal, las fechas de las reuniones o presentaciones realizadas, la fecha proyectada de cierre según las estimaciones del ejecutivo comercial basadas en las señales de compra del cliente, y la fecha real de cierre cuando la oportunidad se materializa en contrato firmado. Se documenta el tiempo total transcurrido desde el primer contacto hasta el cierre expresado en días calendario para calcular métricas de velocidad del ciclo de ventas y eficiencia del proceso comercial.
-Se registran observaciones narrativas extensas y detalladas sobre cada actividad comercial donde el ejecutivo responsable documenta información cualitativa relevante como el contexto del contacto inicial, las necesidades específicas expresadas por el cliente, los pain points o problemas que el cliente busca resolver mediante la contratación del servicio, las objeciones o preocupaciones manifestadas por el cliente durante la negociación, los argumentos de venta que resultaron más efectivos para superar objeciones, las referencias comerciales solicitadas y proporcionadas, los competidores que el cliente está evaluando en paralelo, los factores diferenciadores que el cliente valora de la propuesta de Anaconda Web, las condiciones comerciales especiales negociadas cuando aplica, los compromisos de tiempos de entrega acordados, las expectativas del cliente sobre el servicio post venta, la percepción del cliente sobre la certificación ISO 27001:2022 como factor de decisión, las lecciones aprendidas del proceso comercial que pueden ser aplicadas en futuras oportunidades similares, y cualquier información adicional que contribuya a construir un perfil completo y profundo del cliente y la oportunidad de negocio.
-Este sistema de registro es revisado semanalmente por la Gerencia de Ventas y Soporte Técnico liderada por Juan Andrés Rojas para el seguimiento operativo del pipeline y la asignación de recursos comerciales. Es revisado mensualmente por la Gerencia de Operaciones liderada por Mauricio Antonio Colomera Villarroel para la evaluación del cumplimiento de objetivos estratégicos y la toma de decisiones de alto nivel. Es revisado trimestralmente por la Gerencia General para la evaluación de la salud financiera de la empresa y la proyección de ingresos futuros. Es auditado semestralmente por Auditorex Chile SPA como parte de las auditorías internas del SGSI para verificar el cumplimiento de las políticas y procedimientos establecidos. Es auditado anualmente por LOT Internacional como parte de las auditorías de certificación y seguimiento ISO 27001:2022 para verificar la conformidad con los requisitos de la norma internacional.
-La información contenida en este registro es clasificada como de Uso Interno conforme a la Política de Clasificación de la Información de Anaconda Web y debe ser manejada con las medidas de seguridad correspondientes a dicho nivel de clasificación incluyendo almacenamiento en sistemas con control de acceso basado en roles, cifrado de datos en reposo y en tránsito, copias de seguridad diarias con retención de treinta días, registro de auditoría de todos los accesos y modificaciones al archivo, y restricción de distribución únicamente al personal autorizado mediante lista de distribución controlada. Cualquier divulgación no autorizada de la información contenida en este registro constituye una violación de las políticas de seguridad de la información y puede resultar en acciones disciplinarias conforme al reglamento interno de trabajo de Anaconda Web.
-Los datos registrados en este sistema son utilizados para múltiples propósitos analíticos y de inteligencia de negocios incluyendo el cálculo de métricas clave de desempeño comercial KPIs como tasa de conversión de leads a oportunidades, tasa de conversión de oportunidades a contratos cerrados ganados, valor promedio de oportunidad por ejecutivo comercial, valor promedio de contrato cerrado, duración promedio del ciclo de ventas por tipo de producto, efectividad relativa de cada canal de contacto medida por tasa de conversión, retorno de inversión ROI de las actividades de marketing y generación de leads, precisión de las proyecciones de cierre mediante comparación de fechas proyectadas versus reales, y evolución temporal del pipeline comercial mediante análisis de tendencias mes a mes. Estos análisis son fundamentales para la planificación estratégica de la empresa, la asignación eficiente de recursos comerciales y de marketing, la identificación de oportunidades de capacitación del equipo de ventas, la definición de objetivos realistas y desafiantes, y la mejora continua de los procesos comerciales conforme a la filosofía de calidad total y ciclo PDCA implementada en el marco del SGSI ISO 27001:2022.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>REGISTRO DETALLADO DE ACTIVIDADES COMERCIALES - BASE DE DATOS COMPLETA</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="55" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>ID Actividad</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Fecha Registro</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Cliente / Prospecto</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>RUT Tributario</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Sector Industrial</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>Ejecutivo Comercial Responsable</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Cargo Ejecutivo</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>Tipo de Actividad Comercial</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Producto/Servicio Detallado</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>Valor USD</t>
-        </is>
-      </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>Moneda</t>
-        </is>
-      </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>Estado Pipeline</t>
-        </is>
-      </c>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>Canal Contacto</t>
-        </is>
-      </c>
-      <c r="N19" s="10" t="inlineStr">
-        <is>
-          <t>Prioridad Estratégica</t>
-        </is>
-      </c>
-      <c r="O19" s="10" t="inlineStr">
-        <is>
-          <t>Fecha Cierre Proyectada</t>
-        </is>
-      </c>
-      <c r="P19" s="10" t="inlineStr">
-        <is>
-          <t>Fecha Cierre Real</t>
-        </is>
-      </c>
-      <c r="Q19" s="10" t="inlineStr">
-        <is>
-          <t>Días Ciclo Ventas</t>
-        </is>
-      </c>
-      <c r="R19" s="10" t="inlineStr">
-        <is>
-          <t>Observaciones Detalladas del Proceso Comercial</t>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Contenido del documento</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Metadata y Propósito</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Información detallada y alcance del registro</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Registro de Actividades</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Base de datos completa de actividades comerciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Estadísticas y Análisis</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Métricas, KPIs y análisis de desempeño</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Metodología</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Procedimientos y controles ISO 27001:2022</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="M10:R10"/>
-    <mergeCell ref="A16:R16"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M13:R13"/>
-    <mergeCell ref="M12:R12"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="A3:R3"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A5:R5"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E7:J7"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A4:R4"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="M9:R9"/>
-    <mergeCell ref="K7:R7"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M11:R11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/evidencias/excel/01_Registro_Actividades_Comerciales.xlsx
+++ b/evidencias/excel/01_Registro_Actividades_Comerciales.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Índice" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metadata y Propósito" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Registro de Actividades" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -103,6 +105,22 @@
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -143,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,6 +210,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -827,8 +854,8 @@
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A22:J22"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A22:J22"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="A4:J4"/>
@@ -997,4 +1024,164 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>PROPÓSITO, ALCANCE Y METODOLOGÍA DEL REGISTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="800" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>FUNDAMENTO Y JUSTIFICACIÓN DEL REGISTRO DE ACTIVIDADES COMERCIALES
+Este registro constituye uno de los pilares fundamentales del Sistema de Gestión de Seguridad de la Información implementado por Anaconda Web bajo la norma internacional ISO/IEC 27001:2022. Su elaboración responde a múltiples requisitos normativos y necesidades operacionales de la organización que se detallan exhaustivamente en los párrafos subsiguientes.
+CUMPLIMIENTO DE REQUISITOS NORMATIVOS ISO 27001:2022
+La norma internacional ISO/IEC 27001:2022 establece en su cláusula 7.5 sobre información documentada que las organizaciones deben determinar la información documentada necesaria para la eficacia del Sistema de Gestión de Seguridad de la Información. En particular, el Anexo A de controles de seguridad establece múltiples controles relacionados con la gestión de activos de información, las relaciones con clientes y proveedores, y la trazabilidad de procesos de negocio. Este registro da cumplimiento específico a los siguientes controles: Control A.5.9 sobre inventario de activos de información donde los datos de clientes y oportunidades comerciales constituyen activos críticos de información que deben ser identificados, clasificados y protegidos. Control A.5.10 sobre uso aceptable de información que requiere documentar cómo se utiliza la información comercial sensible. Control A.5.15 sobre control de acceso que requiere trazabilidad de quién accede a información de clientes. Control A.8.10 sobre eliminación de información que requiere retención controlada de registros comerciales.
+TRAZABILIDAD INTEGRAL DEL PROCESO COMERCIAL
+El sistema de registro implementado permite mantener trazabilidad completa end-to-end de todo el ciclo de vida de cada oportunidad comercial desde el primer contacto con el prospecto hasta el cierre definitivo de la oportunidad ya sea como contrato ganado o como oportunidad perdida. Esta trazabilidad integral es crítica para múltiples propósitos organizacionales: permite reconstruir históricam  ente todo el proceso comercial ante auditorías internas o externas, facilita la transferencia de conocimiento entre ejecutivos comerciales cuando se realizan cambios de responsabilidad de cuentas, proporciona datos objetivos para resolución de disputas o malentendidos con clientes, permite análisis forense de oportunidades perdidas para identificar causas raíz de pérdida de negocio, y documenta evidencia de cumplimiento de compromisos comerciales ante requerimientos legales o regulatorios.
+Cada registro individual documenta no solamente los datos básicos de identificación del cliente y la oportunidad sino también información contextual rica sobre el proceso de venta incluyendo los pain points específicos que motivaron al cliente a buscar una solución, las objeciones que el cliente manifestó durante el proceso de evaluación, los argumentos de venta que resultaron efectivos para superar dichas objeciones, los competidores que el cliente evaluó en paralelo, los factores diferenciadores que finalmente determinaron la decisión de compra, y las lecciones aprendidas que pueden ser aplicadas en futuras oportunidades similares.
+EVALUACIÓN OBJETIVA DEL DESEMPEÑO COMERCIAL
+El registro proporciona datos cuantitativos objetivos que permiten evaluar el desempeño del área comercial tanto a nivel individual de cada ejecutivo como a nivel agregado del equipo completo. Las métricas que pueden ser calculadas a partir de los datos registrados incluyen: tasa de conversión de prospectos iniciales a leads calificados, tasa de conversión de leads calificados a oportunidades activas con propuesta enviada, tasa de conversión de oportunidades a contratos cerrados ganados, valor promedio de oportunidad por ejecutivo comercial, valor promedio de contrato cerrado, duración promedio del ciclo de ventas medido en días desde primer contacto hasta cierre, velocidad de pipeline medida como valor de nuevas oportunidades ingresadas por mes, precisión de proyecciones de cierre mediante comparación de fechas proyectadas versus fechas reales de cierre, efectividad relativa de cada canal de contacto medida por tasa de conversión, retorno de inversión de actividades de marketing medido como costo por lead adquirido versus valor lifetime del cliente.
+Estas métricas objetivas basadas en datos reales permiten tomar decisiones gerenciales fundamentadas en evidencia en lugar de intuición o percepción subjetiva. Por ejemplo, si los datos muestran que las oportunidades generadas a través de referidos de clientes existentes tienen una tasa de conversión del noventa por ciento mientras que las oportunidades generadas a través de marketing digital tienen una tasa de conversión del treinta por ciento, la gerencia puede decidir invertir más recursos en programas de referidos y menos en marketing digital. Si los datos muestran que un ejecutivo comercial específico tiene una tasa de conversión significativamente inferior al promedio del equipo, la gerencia puede decidir proporcionar capacitación adicional o coaching personalizado a dicho ejecutivo.
+PROTECCIÓN DE INFORMACIÓN COMERCIAL SENSIBLE
+La información contenida en este registro es clasificada como Uso Interno conforme a la Política de Clasificación de la Información de Anaconda Web. Esta clasificación implica que la información no es de carácter público y no debe ser divulgada a personas externas a la organización sin autorización explícita de la gerencia. La divulgación no autorizada de esta información podría causar daño a Anaconda Web de múltiples formas: los competidores podrían obtener inteligencia sobre las estrategias comerciales, estructuras de precios, descuentos ofrecidos y argumentos de venta utilizados por Anaconda Web. Los clientes actuales podrían sentirse incómodos si descubren que su información de contacto y requerimientos específicos está siendo registrada y analizada. Los prospectos que están en proceso de evaluación podrían decidir no contratar si perciben que Anaconda Web no protege adecuadamente la confidencialidad de las conversaciones comerciales.
+Por estas razones, el acceso a este registro está restringido mediante controles de acceso basados en roles implementados en los sistemas informáticos de Anaconda Web. Solo el personal con necesidad legítima de conocer puede acceder al registro completo. Los ejecutivos comerciales tienen acceso solamente a sus propias oportunidades pero no a las oportunidades de otros ejecutivos para proteger la confidencialidad de la información comercial entre colegas. Los gerentes tienen acceso completo al registro para propósitos de supervisión y evaluación de desempeño. El personal de auditoría interna y externa tiene acceso completo para propósitos de verificación de cumplimiento normativo.
+GESTIÓN DE RIESGOS EN RELACIONES COMERCIALES
+El registro de actividades comerciales es también una herramienta fundamental para la gestión de riesgos asociados a las relaciones con clientes conforme al control A.5.19 de ISO 27001:2022 sobre identificación de riesgos relacionados con proveedores y clientes. Durante el proceso comercial, los ejecutivos documentan señales de alerta o red flags que puedan indicar riesgos potenciales en la relación comercial. Por ejemplo, si un cliente solicita descuentos excesivamente agresivos que no son razonables para el tamaño del proyecto, esto puede indicar que el cliente tiene problemas financieros y existe riesgo de morosidad en los pagos futuros. Si un cliente solicita condiciones contractuales inusuales como plazos de pago extremadamente extensos o cláusulas de penalización desproporcionadas, esto puede indicar que el cliente ha tenido experiencias negativas con proveedores anteriores y existe riesgo de conflictos futuros. Si un cliente cambia frecuentemente de proveedor de servicios tecnológicos, esto puede indicar que el cliente es difícil de satisfacer y existe riesgo de cancelación prematura del contrato.
+La documentación de estos riesgos potenciales en el registro permite a la gerencia tomar decisiones informadas sobre si aceptar o rechazar ciertos clientes, qué condiciones comerciales ofrecer para mitigar los riesgos identificados, y qué garantías adicionales solicitar antes de iniciar la prestación de servicios. Esta gestión proactiva de riesgos protege a Anaconda Web de relaciones comerciales potencialmente problemáticas que podrían resultar en pérdidas financieras, daño reputacional o consumo excesivo de recursos gerenciales en la gestión de conflictos.
+MEJORA CONTINUA DEL PROCESO COMERCIAL
+Conforme a la filosofía de mejora continua inherente a ISO 27001:2022 y materializada en el ciclo Planificar-Hacer-Verificar-Actuar (PDCA), el registro de actividades comerciales proporciona los datos necesarios para identificar oportunidades de mejora en los procesos comerciales de Anaconda Web. El análisis periódico de los datos registrados permite responder preguntas estratégicas como: ¿Cuáles son los cuellos de botella más frecuentes en nuestro proceso de ventas? ¿En qué etapa del proceso perdemos más oportunidades? ¿Qué objeciones de los clientes son más difíciles de superar? ¿Qué argumentos de venta son más efectivos? ¿Qué características de nuestros productos valoran más los clientes? ¿Qué mejoras podríamos implementar para acortar el ciclo de ventas? ¿Qué capacitación adicional necesita nuestro equipo comercial?
+Las respuestas a estas preguntas derivadas del análisis de datos reales permiten implementar mejoras específicas y medibles en el proceso comercial. Por ejemplo, si el análisis muestra que las oportunidades se demoran excesivamente en la etapa de elaboración de propuesta técnica, Anaconda Web puede decidir invertir en la creación de plantillas estandarizadas de propuestas que aceleren este proceso. Si el análisis muestra que los clientes frecuentemente solicitan características que no están incluidas en los productos estándar, Anaconda Web puede decidir desarrollar nuevos productos o servicios que incorporen dichas características. Si el análisis muestra que los ejecutivos comerciales tienen dificultad para articular el valor de la certificación ISO 27001:2022, Anaconda Web puede decidir desarrollar material de ventas específico que explique este diferenciador de manera clara y convincente.
+Este documento es revisado y actualizado continuamente para reflejar la realidad operativa de Anaconda Web y cumplir con los requisitos de auditoría de LOT Internacional.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>RUT</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>Tipo Actividad</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>Producto/Servicio</t>
+        </is>
+      </c>
+      <c r="J1" s="20" t="inlineStr">
+        <is>
+          <t>Valor USD</t>
+        </is>
+      </c>
+      <c r="K1" s="20" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="L1" s="20" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="M1" s="20" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="N1" s="20" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="O1" s="20" t="inlineStr">
+        <is>
+          <t>F. Proyectada</t>
+        </is>
+      </c>
+      <c r="P1" s="20" t="inlineStr">
+        <is>
+          <t>F. Real</t>
+        </is>
+      </c>
+      <c r="Q1" s="20" t="inlineStr">
+        <is>
+          <t>Días</t>
+        </is>
+      </c>
+      <c r="R1" s="20" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>